--- a/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBarNegative.xlsx
+++ b/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBarNegative.xlsx
@@ -408,7 +408,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e40ff61a-5a84-44d4-be7e-3853bfd4dca8}</x14:id>
+          <x14:id>{2a0b837d-a043-4814-be7f-02dccca0404c}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -422,7 +422,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{358dffa1-56c8-4c78-92b0-c2d4055cbf98}</x14:id>
+          <x14:id>{eebd3184-fef2-41c4-abfd-02f3c9ee9560}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -436,7 +436,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e40ff61a-5a84-44d4-be7e-3853bfd4dca8}">
+          <x14:cfRule type="dataBar" id="{2a0b837d-a043-4814-be7f-02dccca0404c}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -451,7 +451,7 @@
           <xm:sqref>A1:A4</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{358dffa1-56c8-4c78-92b0-c2d4055cbf98}">
+          <x14:cfRule type="dataBar" id="{eebd3184-fef2-41c4-abfd-02f3c9ee9560}">
             <x14:dataBar minLength="0" maxLength="100" showValue="0" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>-100</xm:f>

--- a/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBarNegative.xlsx
+++ b/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBarNegative.xlsx
@@ -408,7 +408,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2a0b837d-a043-4814-be7f-02dccca0404c}</x14:id>
+          <x14:id>{ba51641a-8cad-4020-ac9f-9887ac308304}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -422,7 +422,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eebd3184-fef2-41c4-abfd-02f3c9ee9560}</x14:id>
+          <x14:id>{c4f0765a-4f73-4119-8291-090caa213f96}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -436,7 +436,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2a0b837d-a043-4814-be7f-02dccca0404c}">
+          <x14:cfRule type="dataBar" id="{ba51641a-8cad-4020-ac9f-9887ac308304}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -451,7 +451,7 @@
           <xm:sqref>A1:A4</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eebd3184-fef2-41c4-abfd-02f3c9ee9560}">
+          <x14:cfRule type="dataBar" id="{c4f0765a-4f73-4119-8291-090caa213f96}">
             <x14:dataBar minLength="0" maxLength="100" showValue="0" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>-100</xm:f>
